--- a/outputs/entities/FX-Netting-L_6129_DE-2026-08-24.xlsx
+++ b/outputs/entities/FX-Netting-L_6129_DE-2026-08-24.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Netting" sheetId="1" r:id="Rc14db9024adf4579"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Details" sheetId="2" r:id="Ra8260f7741fc41d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Netting" sheetId="1" r:id="R00751257f9aa4b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Details" sheetId="2" r:id="R9b5ecb42e12a4d7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -301,7 +301,6 @@
     <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="10" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="20" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -313,18 +312,16 @@
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
-      <x:c r="G1" s="2"/>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4" t="str">
-        <x:v>Summierung der FX-Geschäfte | Quelle: GitHub Issue #2 | 78 Geschäfte</x:v>
+        <x:v>Summierung von „Diff. in GC“ | Quelle: GitHub Issue #2 | 78 Geschäfte</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
       <x:c r="D2" s="4"/>
       <x:c r="E2" s="4"/>
       <x:c r="F2" s="4"/>
-      <x:c r="G2" s="4"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="6" t="str">
@@ -343,10 +340,7 @@
         <x:v>Deals</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
-        <x:v>Net Amount</x:v>
-      </x:c>
-      <x:c r="G4" s="6" t="str">
-        <x:v>Net EUR Equivalent</x:v>
+        <x:v>Sum Diff. in GC</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -367,12 +361,8 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A5,'Details'!$C$2:$C$79,B5,'Details'!$E$2:$E$79,C5,'Details'!$H$2:$H$79,D5)</x:f>
-        <x:v>350000</x:v>
-      </x:c>
-      <x:c r="G5" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A5,'Details'!$C$2:$C$79,B5,'Details'!$E$2:$E$79,C5,'Details'!$H$2:$H$79,D5)</x:f>
-        <x:v>-212519.85</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A5,'Details'!$C$2:$C$79,B5,'Details'!$E$2:$E$79,C5,'Details'!$H$2:$H$79,D5)</x:f>
+        <x:v>401.43</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -393,12 +383,8 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="F6" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A6,'Details'!$C$2:$C$79,B6,'Details'!$E$2:$E$79,C6,'Details'!$H$2:$H$79,D6)</x:f>
-        <x:v>38600000</x:v>
-      </x:c>
-      <x:c r="G6" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A6,'Details'!$C$2:$C$79,B6,'Details'!$E$2:$E$79,C6,'Details'!$H$2:$H$79,D6)</x:f>
-        <x:v>-5001257.340000002</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A6,'Details'!$C$2:$C$79,B6,'Details'!$E$2:$E$79,C6,'Details'!$H$2:$H$79,D6)</x:f>
+        <x:v>-86439.01999999997</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -419,12 +405,8 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A7,'Details'!$C$2:$C$79,B7,'Details'!$E$2:$E$79,C7,'Details'!$H$2:$H$79,D7)</x:f>
-        <x:v>-2000000</x:v>
-      </x:c>
-      <x:c r="G7" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A7,'Details'!$C$2:$C$79,B7,'Details'!$E$2:$E$79,C7,'Details'!$H$2:$H$79,D7)</x:f>
-        <x:v>82487.83</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A7,'Details'!$C$2:$C$79,B7,'Details'!$E$2:$E$79,C7,'Details'!$H$2:$H$79,D7)</x:f>
+        <x:v>-317.62</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -445,12 +427,8 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F8" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A8,'Details'!$C$2:$C$79,B8,'Details'!$E$2:$E$79,C8,'Details'!$H$2:$H$79,D8)</x:f>
-        <x:v>-1260000</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A8,'Details'!$C$2:$C$79,B8,'Details'!$E$2:$E$79,C8,'Details'!$H$2:$H$79,D8)</x:f>
-        <x:v>1472094.32</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A8,'Details'!$C$2:$C$79,B8,'Details'!$E$2:$E$79,C8,'Details'!$H$2:$H$79,D8)</x:f>
+        <x:v>2278.0400000000004</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -471,12 +449,8 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A9,'Details'!$C$2:$C$79,B9,'Details'!$E$2:$E$79,C9,'Details'!$H$2:$H$79,D9)</x:f>
-        <x:v>19100000</x:v>
-      </x:c>
-      <x:c r="G9" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A9,'Details'!$C$2:$C$79,B9,'Details'!$E$2:$E$79,C9,'Details'!$H$2:$H$79,D9)</x:f>
-        <x:v>-2133106.81</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A9,'Details'!$C$2:$C$79,B9,'Details'!$E$2:$E$79,C9,'Details'!$H$2:$H$79,D9)</x:f>
+        <x:v>-48500.14000000001</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -497,12 +471,8 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A10,'Details'!$C$2:$C$79,B10,'Details'!$E$2:$E$79,C10,'Details'!$H$2:$H$79,D10)</x:f>
-        <x:v>67600000</x:v>
-      </x:c>
-      <x:c r="G10" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A10,'Details'!$C$2:$C$79,B10,'Details'!$E$2:$E$79,C10,'Details'!$H$2:$H$79,D10)</x:f>
-        <x:v>-620346.3</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A10,'Details'!$C$2:$C$79,B10,'Details'!$E$2:$E$79,C10,'Details'!$H$2:$H$79,D10)</x:f>
+        <x:v>-15687.02</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -523,12 +493,8 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F11" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A11,'Details'!$C$2:$C$79,B11,'Details'!$E$2:$E$79,C11,'Details'!$H$2:$H$79,D11)</x:f>
-        <x:v>670000000</x:v>
-      </x:c>
-      <x:c r="G11" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A11,'Details'!$C$2:$C$79,B11,'Details'!$E$2:$E$79,C11,'Details'!$H$2:$H$79,D11)</x:f>
-        <x:v>-409535.45</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A11,'Details'!$C$2:$C$79,B11,'Details'!$E$2:$E$79,C11,'Details'!$H$2:$H$79,D11)</x:f>
+        <x:v>1235.33</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -549,12 +515,8 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F12" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A12,'Details'!$C$2:$C$79,B12,'Details'!$E$2:$E$79,C12,'Details'!$H$2:$H$79,D12)</x:f>
-        <x:v>300000</x:v>
-      </x:c>
-      <x:c r="G12" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A12,'Details'!$C$2:$C$79,B12,'Details'!$E$2:$E$79,C12,'Details'!$H$2:$H$79,D12)</x:f>
-        <x:v>-69670.23</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A12,'Details'!$C$2:$C$79,B12,'Details'!$E$2:$E$79,C12,'Details'!$H$2:$H$79,D12)</x:f>
+        <x:v>-206.49</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -575,12 +537,8 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="F13" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A13,'Details'!$C$2:$C$79,B13,'Details'!$E$2:$E$79,C13,'Details'!$H$2:$H$79,D13)</x:f>
-        <x:v>950000</x:v>
-      </x:c>
-      <x:c r="G13" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A13,'Details'!$C$2:$C$79,B13,'Details'!$E$2:$E$79,C13,'Details'!$H$2:$H$79,D13)</x:f>
-        <x:v>-220514.84</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A13,'Details'!$C$2:$C$79,B13,'Details'!$E$2:$E$79,C13,'Details'!$H$2:$H$79,D13)</x:f>
+        <x:v>-3638.44</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -601,12 +559,8 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F14" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A14,'Details'!$C$2:$C$79,B14,'Details'!$E$2:$E$79,C14,'Details'!$H$2:$H$79,D14)</x:f>
-        <x:v>-370000</x:v>
-      </x:c>
-      <x:c r="G14" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A14,'Details'!$C$2:$C$79,B14,'Details'!$E$2:$E$79,C14,'Details'!$H$2:$H$79,D14)</x:f>
-        <x:v>250469.78</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A14,'Details'!$C$2:$C$79,B14,'Details'!$E$2:$E$79,C14,'Details'!$H$2:$H$79,D14)</x:f>
+        <x:v>1479.19</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -627,12 +581,8 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F15" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A15,'Details'!$C$2:$C$79,B15,'Details'!$E$2:$E$79,C15,'Details'!$H$2:$H$79,D15)</x:f>
-        <x:v>12500000</x:v>
-      </x:c>
-      <x:c r="G15" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A15,'Details'!$C$2:$C$79,B15,'Details'!$E$2:$E$79,C15,'Details'!$H$2:$H$79,D15)</x:f>
-        <x:v>-328620.18</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A15,'Details'!$C$2:$C$79,B15,'Details'!$E$2:$E$79,C15,'Details'!$H$2:$H$79,D15)</x:f>
+        <x:v>-3505.74</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -653,12 +603,8 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F16" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A16,'Details'!$C$2:$C$79,B16,'Details'!$E$2:$E$79,C16,'Details'!$H$2:$H$79,D16)</x:f>
-        <x:v>16000000</x:v>
-      </x:c>
-      <x:c r="G16" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A16,'Details'!$C$2:$C$79,B16,'Details'!$E$2:$E$79,C16,'Details'!$H$2:$H$79,D16)</x:f>
-        <x:v>-436523.24</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A16,'Details'!$C$2:$C$79,B16,'Details'!$E$2:$E$79,C16,'Details'!$H$2:$H$79,D16)</x:f>
+        <x:v>-7026.36</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -679,18 +625,14 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="F17" s="9" t="n">
-        <x:f>SUMIFS('Details'!$I$2:$I$79,'Details'!$B$2:$B$79,A17,'Details'!$C$2:$C$79,B17,'Details'!$E$2:$E$79,C17,'Details'!$H$2:$H$79,D17)</x:f>
-        <x:v>2770000</x:v>
-      </x:c>
-      <x:c r="G17" s="9" t="n">
-        <x:f>SUMIFS('Details'!$L$2:$L$79,'Details'!$B$2:$B$79,A17,'Details'!$C$2:$C$79,B17,'Details'!$E$2:$E$79,C17,'Details'!$H$2:$H$79,D17)</x:f>
-        <x:v>-2414116.75</x:v>
+        <x:f>SUMIFS('Details'!$N$2:$N$79,'Details'!$B$2:$B$79,A17,'Details'!$C$2:$C$79,B17,'Details'!$E$2:$E$79,C17,'Details'!$H$2:$H$79,D17)</x:f>
+        <x:v>-42744.439999999995</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A1:G1"/>
-    <x:mergeCell ref="A2:G2"/>
+    <x:mergeCell ref="A1:F1"/>
+    <x:mergeCell ref="A2:F2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/outputs/entities/FX-Netting-L_6129_DE-2026-08-24.xlsx
+++ b/outputs/entities/FX-Netting-L_6129_DE-2026-08-24.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Netting" sheetId="1" r:id="R00751257f9aa4b4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Details" sheetId="2" r:id="R9b5ecb42e12a4d7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Netting" sheetId="1" r:id="R5284e4cf494b4c65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Details" sheetId="2" r:id="R5b2e5e4474d74d2d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,10 +16,10 @@
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="3">
     <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
-    <x:numFmt numFmtId="201" formatCode="#,##0.00;[Red](#,##0.00);-"/>
+    <x:numFmt numFmtId="201" formatCode="#,##0.00;[Red]-#,##0.00;-"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
   </x:numFmts>
-  <x:fonts count="4">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -39,6 +39,11 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
@@ -65,13 +70,18 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="1">
+  <x:borders count="2">
     <x:border/>
+    <x:border>
+      <x:top style="medium">
+        <x:color rgb="FF17365D"/>
+      </x:top>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -84,6 +94,9 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="201" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -629,10 +642,24 @@
         <x:v>-42744.439999999995</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="11" t="str">
+        <x:v>Summe Diff. in GC</x:v>
+      </x:c>
+      <x:c r="B18" s="11"/>
+      <x:c r="C18" s="11"/>
+      <x:c r="D18" s="11"/>
+      <x:c r="E18" s="11"/>
+      <x:c r="F18" s="12" t="n">
+        <x:f>SUM(F5:F17)</x:f>
+        <x:v>-202671.27999999997</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
     <x:mergeCell ref="A2:F2"/>
+    <x:mergeCell ref="A18:E18"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -661,52 +688,52 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="13" t="str">
+      <x:c r="A1" s="16" t="str">
         <x:v>Reference</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="str">
+      <x:c r="B1" s="16" t="str">
         <x:v>Entity</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="str">
+      <x:c r="C1" s="16" t="str">
         <x:v>Counterparty</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="str">
+      <x:c r="D1" s="16" t="str">
         <x:v>Int/Ext</x:v>
       </x:c>
-      <x:c r="E1" s="13" t="str">
+      <x:c r="E1" s="16" t="str">
         <x:v>Value Date</x:v>
       </x:c>
-      <x:c r="F1" s="13" t="str">
+      <x:c r="F1" s="16" t="str">
         <x:v>Deal Type</x:v>
       </x:c>
-      <x:c r="G1" s="13" t="str">
+      <x:c r="G1" s="16" t="str">
         <x:v>Buy/Sell</x:v>
       </x:c>
-      <x:c r="H1" s="13" t="str">
+      <x:c r="H1" s="16" t="str">
         <x:v>Currency</x:v>
       </x:c>
-      <x:c r="I1" s="13" t="str">
+      <x:c r="I1" s="16" t="str">
         <x:v>Amount</x:v>
       </x:c>
-      <x:c r="J1" s="13" t="str">
+      <x:c r="J1" s="16" t="str">
         <x:v>Rate</x:v>
       </x:c>
-      <x:c r="K1" s="13" t="str">
+      <x:c r="K1" s="16" t="str">
         <x:v>Equivalent Currency</x:v>
       </x:c>
-      <x:c r="L1" s="13" t="str">
+      <x:c r="L1" s="16" t="str">
         <x:v>Equivalent Amount EUR</x:v>
       </x:c>
-      <x:c r="M1" s="13" t="str">
+      <x:c r="M1" s="16" t="str">
         <x:v>Mark-to-market</x:v>
       </x:c>
-      <x:c r="N1" s="13" t="str">
+      <x:c r="N1" s="16" t="str">
         <x:v>Diff. in GC</x:v>
       </x:c>
-      <x:c r="O1" s="13" t="str">
+      <x:c r="O1" s="16" t="str">
         <x:v>Amount (MTM) EUR</x:v>
       </x:c>
-      <x:c r="P1" s="13" t="str">
+      <x:c r="P1" s="16" t="str">
         <x:v>Portfolio</x:v>
       </x:c>
     </x:row>
@@ -738,7 +765,7 @@
       <x:c r="I2" s="9" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="J2" s="14" t="n">
+      <x:c r="J2" s="17" t="n">
         <x:v>1.1432</x:v>
       </x:c>
       <x:c r="K2" t="str">
@@ -788,7 +815,7 @@
       <x:c r="I3" s="9" t="n">
         <x:v>1500000</x:v>
       </x:c>
-      <x:c r="J3" s="14" t="n">
+      <x:c r="J3" s="17" t="n">
         <x:v>7.7235</x:v>
       </x:c>
       <x:c r="K3" t="str">
@@ -838,7 +865,7 @@
       <x:c r="I4" s="9" t="n">
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="J4" s="14" t="n">
+      <x:c r="J4" s="17" t="n">
         <x:v>7.7398</x:v>
       </x:c>
       <x:c r="K4" t="str">
@@ -888,7 +915,7 @@
       <x:c r="I5" s="9" t="n">
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="J5" s="14" t="n">
+      <x:c r="J5" s="17" t="n">
         <x:v>8.9713</x:v>
       </x:c>
       <x:c r="K5" t="str">
@@ -938,7 +965,7 @@
       <x:c r="I6" s="9" t="n">
         <x:v>2000000</x:v>
       </x:c>
-      <x:c r="J6" s="14" t="n">
+      <x:c r="J6" s="17" t="n">
         <x:v>7.7327</x:v>
       </x:c>
       <x:c r="K6" t="str">
@@ -988,7 +1015,7 @@
       <x:c r="I7" s="9" t="n">
         <x:v>2000000</x:v>
       </x:c>
-      <x:c r="J7" s="14" t="n">
+      <x:c r="J7" s="17" t="n">
         <x:v>8.9481</x:v>
       </x:c>
       <x:c r="K7" t="str">
@@ -1038,7 +1065,7 @@
       <x:c r="I8" s="9" t="n">
         <x:v>280000</x:v>
       </x:c>
-      <x:c r="J8" s="14" t="n">
+      <x:c r="J8" s="17" t="n">
         <x:v>1.144947</x:v>
       </x:c>
       <x:c r="K8" t="str">
@@ -1088,7 +1115,7 @@
       <x:c r="I9" s="9" t="n">
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="J9" s="14" t="n">
+      <x:c r="J9" s="17" t="n">
         <x:v>8.9542</x:v>
       </x:c>
       <x:c r="K9" t="str">
@@ -1138,7 +1165,7 @@
       <x:c r="I10" s="9" t="n">
         <x:v>2200000</x:v>
       </x:c>
-      <x:c r="J10" s="14" t="n">
+      <x:c r="J10" s="17" t="n">
         <x:v>7.7411</x:v>
       </x:c>
       <x:c r="K10" t="str">
@@ -1188,7 +1215,7 @@
       <x:c r="I11" s="9" t="n">
         <x:v>-120000</x:v>
       </x:c>
-      <x:c r="J11" s="14" t="n">
+      <x:c r="J11" s="17" t="n">
         <x:v>0.8561</x:v>
       </x:c>
       <x:c r="K11" t="str">
@@ -1238,7 +1265,7 @@
       <x:c r="I12" s="9" t="n">
         <x:v>2000000</x:v>
       </x:c>
-      <x:c r="J12" s="14" t="n">
+      <x:c r="J12" s="17" t="n">
         <x:v>7.7375</x:v>
       </x:c>
       <x:c r="K12" t="str">
@@ -1288,7 +1315,7 @@
       <x:c r="I13" s="9" t="n">
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="J13" s="14" t="n">
+      <x:c r="J13" s="17" t="n">
         <x:v>8.9387</x:v>
       </x:c>
       <x:c r="K13" t="str">
@@ -1338,7 +1365,7 @@
       <x:c r="I14" s="9" t="n">
         <x:v>-100000</x:v>
       </x:c>
-      <x:c r="J14" s="14" t="n">
+      <x:c r="J14" s="17" t="n">
         <x:v>1.4775</x:v>
       </x:c>
       <x:c r="K14" t="str">
@@ -1388,7 +1415,7 @@
       <x:c r="I15" s="9" t="n">
         <x:v>-100000</x:v>
       </x:c>
-      <x:c r="J15" s="14" t="n">
+      <x:c r="J15" s="17" t="n">
         <x:v>0.858</x:v>
       </x:c>
       <x:c r="K15" t="str">
@@ -1438,7 +1465,7 @@
       <x:c r="I16" s="9" t="n">
         <x:v>250000</x:v>
       </x:c>
-      <x:c r="J16" s="14" t="n">
+      <x:c r="J16" s="17" t="n">
         <x:v>1.143143</x:v>
       </x:c>
       <x:c r="K16" t="str">
@@ -1488,7 +1515,7 @@
       <x:c r="I17" s="9" t="n">
         <x:v>1700000</x:v>
       </x:c>
-      <x:c r="J17" s="14" t="n">
+      <x:c r="J17" s="17" t="n">
         <x:v>8.9472</x:v>
       </x:c>
       <x:c r="K17" t="str">
@@ -1538,7 +1565,7 @@
       <x:c r="I18" s="9" t="n">
         <x:v>800000</x:v>
       </x:c>
-      <x:c r="J18" s="14" t="n">
+      <x:c r="J18" s="17" t="n">
         <x:v>7.755</x:v>
       </x:c>
       <x:c r="K18" t="str">
@@ -1588,7 +1615,7 @@
       <x:c r="I19" s="9" t="n">
         <x:v>2000000</x:v>
       </x:c>
-      <x:c r="J19" s="14" t="n">
+      <x:c r="J19" s="17" t="n">
         <x:v>7.7215</x:v>
       </x:c>
       <x:c r="K19" t="str">
@@ -1638,7 +1665,7 @@
       <x:c r="I20" s="9" t="n">
         <x:v>-150000</x:v>
       </x:c>
-      <x:c r="J20" s="14" t="n">
+      <x:c r="J20" s="17" t="n">
         <x:v>0.8546</x:v>
       </x:c>
       <x:c r="K20" t="str">
@@ -1688,7 +1715,7 @@
       <x:c r="I21" s="9" t="n">
         <x:v>4000000</x:v>
       </x:c>
-      <x:c r="J21" s="14" t="n">
+      <x:c r="J21" s="17" t="n">
         <x:v>37.8</x:v>
       </x:c>
       <x:c r="K21" t="str">
@@ -1738,7 +1765,7 @@
       <x:c r="I22" s="9" t="n">
         <x:v>150000</x:v>
       </x:c>
-      <x:c r="J22" s="14" t="n">
+      <x:c r="J22" s="17" t="n">
         <x:v>1.1435</x:v>
       </x:c>
       <x:c r="K22" t="str">
@@ -1788,7 +1815,7 @@
       <x:c r="I23" s="9" t="n">
         <x:v>1300000</x:v>
       </x:c>
-      <x:c r="J23" s="14" t="n">
+      <x:c r="J23" s="17" t="n">
         <x:v>7.7278</x:v>
       </x:c>
       <x:c r="K23" t="str">
@@ -1838,7 +1865,7 @@
       <x:c r="I24" s="9" t="n">
         <x:v>2000000</x:v>
       </x:c>
-      <x:c r="J24" s="14" t="n">
+      <x:c r="J24" s="17" t="n">
         <x:v>8.9525</x:v>
       </x:c>
       <x:c r="K24" t="str">
@@ -1888,7 +1915,7 @@
       <x:c r="I25" s="9" t="n">
         <x:v>170000</x:v>
       </x:c>
-      <x:c r="J25" s="14" t="n">
+      <x:c r="J25" s="17" t="n">
         <x:v>1.1443</x:v>
       </x:c>
       <x:c r="K25" t="str">
@@ -1938,7 +1965,7 @@
       <x:c r="I26" s="9" t="n">
         <x:v>15000000</x:v>
       </x:c>
-      <x:c r="J26" s="14" t="n">
+      <x:c r="J26" s="17" t="n">
         <x:v>109.36</x:v>
       </x:c>
       <x:c r="K26" t="str">
@@ -1988,7 +2015,7 @@
       <x:c r="I27" s="9" t="n">
         <x:v>10000000</x:v>
       </x:c>
-      <x:c r="J27" s="14" t="n">
+      <x:c r="J27" s="17" t="n">
         <x:v>36.564</x:v>
       </x:c>
       <x:c r="K27" t="str">
@@ -2038,7 +2065,7 @@
       <x:c r="I28" s="9" t="n">
         <x:v>2900000</x:v>
       </x:c>
-      <x:c r="J28" s="14" t="n">
+      <x:c r="J28" s="17" t="n">
         <x:v>7.70405</x:v>
       </x:c>
       <x:c r="K28" t="str">
@@ -2088,7 +2115,7 @@
       <x:c r="I29" s="9" t="n">
         <x:v>-80000</x:v>
       </x:c>
-      <x:c r="J29" s="14" t="n">
+      <x:c r="J29" s="17" t="n">
         <x:v>0.854467</x:v>
       </x:c>
       <x:c r="K29" t="str">
@@ -2138,7 +2165,7 @@
       <x:c r="I30" s="9" t="n">
         <x:v>-240000</x:v>
       </x:c>
-      <x:c r="J30" s="14" t="n">
+      <x:c r="J30" s="17" t="n">
         <x:v>0.855134</x:v>
       </x:c>
       <x:c r="K30" t="str">
@@ -2188,7 +2215,7 @@
       <x:c r="I31" s="9" t="n">
         <x:v>1600000</x:v>
       </x:c>
-      <x:c r="J31" s="14" t="n">
+      <x:c r="J31" s="17" t="n">
         <x:v>8.94619</x:v>
       </x:c>
       <x:c r="K31" t="str">
@@ -2238,7 +2265,7 @@
       <x:c r="I32" s="9" t="n">
         <x:v>200000</x:v>
       </x:c>
-      <x:c r="J32" s="14" t="n">
+      <x:c r="J32" s="17" t="n">
         <x:v>1.142758</x:v>
       </x:c>
       <x:c r="K32" t="str">
@@ -2288,7 +2315,7 @@
       <x:c r="I33" s="9" t="n">
         <x:v>1300000</x:v>
       </x:c>
-      <x:c r="J33" s="14" t="n">
+      <x:c r="J33" s="17" t="n">
         <x:v>7.74765</x:v>
       </x:c>
       <x:c r="K33" t="str">
@@ -2338,7 +2365,7 @@
       <x:c r="I34" s="9" t="n">
         <x:v>-2000000</x:v>
       </x:c>
-      <x:c r="J34" s="14" t="n">
+      <x:c r="J34" s="17" t="n">
         <x:v>24.246</x:v>
       </x:c>
       <x:c r="K34" t="str">
@@ -2388,7 +2415,7 @@
       <x:c r="I35" s="9" t="n">
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="J35" s="14" t="n">
+      <x:c r="J35" s="17" t="n">
         <x:v>7.7268</x:v>
       </x:c>
       <x:c r="K35" t="str">
@@ -2438,7 +2465,7 @@
       <x:c r="I36" s="9" t="n">
         <x:v>110000</x:v>
       </x:c>
-      <x:c r="J36" s="14" t="n">
+      <x:c r="J36" s="17" t="n">
         <x:v>1.14626</x:v>
       </x:c>
       <x:c r="K36" t="str">
@@ -2488,7 +2515,7 @@
       <x:c r="I37" s="9" t="n">
         <x:v>-150000</x:v>
       </x:c>
-      <x:c r="J37" s="14" t="n">
+      <x:c r="J37" s="17" t="n">
         <x:v>1.47762</x:v>
       </x:c>
       <x:c r="K37" t="str">
@@ -2538,7 +2565,7 @@
       <x:c r="I38" s="9" t="n">
         <x:v>2000000</x:v>
       </x:c>
-      <x:c r="J38" s="14" t="n">
+      <x:c r="J38" s="17" t="n">
         <x:v>7.73037</x:v>
       </x:c>
       <x:c r="K38" t="str">
@@ -2588,7 +2615,7 @@
       <x:c r="I39" s="9" t="n">
         <x:v>1300000</x:v>
       </x:c>
-      <x:c r="J39" s="14" t="n">
+      <x:c r="J39" s="17" t="n">
         <x:v>8.95994</x:v>
       </x:c>
       <x:c r="K39" t="str">
@@ -2638,7 +2665,7 @@
       <x:c r="I40" s="9" t="n">
         <x:v>2600000</x:v>
       </x:c>
-      <x:c r="J40" s="14" t="n">
+      <x:c r="J40" s="17" t="n">
         <x:v>7.71601</x:v>
       </x:c>
       <x:c r="K40" t="str">
@@ -2688,7 +2715,7 @@
       <x:c r="I41" s="9" t="n">
         <x:v>1200000</x:v>
       </x:c>
-      <x:c r="J41" s="14" t="n">
+      <x:c r="J41" s="17" t="n">
         <x:v>8.95368</x:v>
       </x:c>
       <x:c r="K41" t="str">
@@ -2738,7 +2765,7 @@
       <x:c r="I42" s="9" t="n">
         <x:v>3000000</x:v>
       </x:c>
-      <x:c r="J42" s="14" t="n">
+      <x:c r="J42" s="17" t="n">
         <x:v>38.307</x:v>
       </x:c>
       <x:c r="K42" t="str">
@@ -2788,7 +2815,7 @@
       <x:c r="I43" s="9" t="n">
         <x:v>2200000</x:v>
       </x:c>
-      <x:c r="J43" s="14" t="n">
+      <x:c r="J43" s="17" t="n">
         <x:v>7.7089</x:v>
       </x:c>
       <x:c r="K43" t="str">
@@ -2838,7 +2865,7 @@
       <x:c r="I44" s="9" t="n">
         <x:v>-100000</x:v>
       </x:c>
-      <x:c r="J44" s="14" t="n">
+      <x:c r="J44" s="17" t="n">
         <x:v>0.8527</x:v>
       </x:c>
       <x:c r="K44" t="str">
@@ -2888,7 +2915,7 @@
       <x:c r="I45" s="9" t="n">
         <x:v>800000</x:v>
       </x:c>
-      <x:c r="J45" s="14" t="n">
+      <x:c r="J45" s="17" t="n">
         <x:v>7.7066</x:v>
       </x:c>
       <x:c r="K45" t="str">
@@ -2938,7 +2965,7 @@
       <x:c r="I46" s="9" t="n">
         <x:v>-100000</x:v>
       </x:c>
-      <x:c r="J46" s="14" t="n">
+      <x:c r="J46" s="17" t="n">
         <x:v>0.8553</x:v>
       </x:c>
       <x:c r="K46" t="str">
@@ -2988,7 +3015,7 @@
       <x:c r="I47" s="9" t="n">
         <x:v>20000000</x:v>
       </x:c>
-      <x:c r="J47" s="14" t="n">
+      <x:c r="J47" s="17" t="n">
         <x:v>110.1</x:v>
       </x:c>
       <x:c r="K47" t="str">
@@ -3038,7 +3065,7 @@
       <x:c r="I48" s="9" t="n">
         <x:v>6000000</x:v>
       </x:c>
-      <x:c r="J48" s="14" t="n">
+      <x:c r="J48" s="17" t="n">
         <x:v>36.803</x:v>
       </x:c>
       <x:c r="K48" t="str">
@@ -3088,7 +3115,7 @@
       <x:c r="I49" s="9" t="n">
         <x:v>250000</x:v>
       </x:c>
-      <x:c r="J49" s="14" t="n">
+      <x:c r="J49" s="17" t="n">
         <x:v>1.143316</x:v>
       </x:c>
       <x:c r="K49" t="str">
@@ -3138,7 +3165,7 @@
       <x:c r="I50" s="9" t="n">
         <x:v>1400000</x:v>
       </x:c>
-      <x:c r="J50" s="14" t="n">
+      <x:c r="J50" s="17" t="n">
         <x:v>7.70153</x:v>
       </x:c>
       <x:c r="K50" t="str">
@@ -3188,7 +3215,7 @@
       <x:c r="I51" s="9" t="n">
         <x:v>2300000</x:v>
       </x:c>
-      <x:c r="J51" s="14" t="n">
+      <x:c r="J51" s="17" t="n">
         <x:v>7.69593</x:v>
       </x:c>
       <x:c r="K51" t="str">
@@ -3238,7 +3265,7 @@
       <x:c r="I52" s="9" t="n">
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="J52" s="14" t="n">
+      <x:c r="J52" s="17" t="n">
         <x:v>8.92066</x:v>
       </x:c>
       <x:c r="K52" t="str">
@@ -3288,7 +3315,7 @@
       <x:c r="I53" s="9" t="n">
         <x:v>2500000</x:v>
       </x:c>
-      <x:c r="J53" s="14" t="n">
+      <x:c r="J53" s="17" t="n">
         <x:v>7.68741</x:v>
       </x:c>
       <x:c r="K53" t="str">
@@ -3338,7 +3365,7 @@
       <x:c r="I54" s="9" t="n">
         <x:v>1500000</x:v>
       </x:c>
-      <x:c r="J54" s="14" t="n">
+      <x:c r="J54" s="17" t="n">
         <x:v>8.92286</x:v>
       </x:c>
       <x:c r="K54" t="str">
@@ -3388,7 +3415,7 @@
       <x:c r="I55" s="9" t="n">
         <x:v>230000</x:v>
       </x:c>
-      <x:c r="J55" s="14" t="n">
+      <x:c r="J55" s="17" t="n">
         <x:v>1.141067</x:v>
       </x:c>
       <x:c r="K55" t="str">
@@ -3438,7 +3465,7 @@
       <x:c r="I56" s="9" t="n">
         <x:v>2500000</x:v>
       </x:c>
-      <x:c r="J56" s="14" t="n">
+      <x:c r="J56" s="17" t="n">
         <x:v>7.6709</x:v>
       </x:c>
       <x:c r="K56" t="str">
@@ -3488,7 +3515,7 @@
       <x:c r="I57" s="9" t="n">
         <x:v>-120000</x:v>
       </x:c>
-      <x:c r="J57" s="14" t="n">
+      <x:c r="J57" s="17" t="n">
         <x:v>0.8568</x:v>
       </x:c>
       <x:c r="K57" t="str">
@@ -3538,7 +3565,7 @@
       <x:c r="I58" s="9" t="n">
         <x:v>3000000</x:v>
       </x:c>
-      <x:c r="J58" s="14" t="n">
+      <x:c r="J58" s="17" t="n">
         <x:v>37.98</x:v>
       </x:c>
       <x:c r="K58" t="str">
@@ -3588,7 +3615,7 @@
       <x:c r="I59" s="9" t="n">
         <x:v>22000000</x:v>
       </x:c>
-      <x:c r="J59" s="14" t="n">
+      <x:c r="J59" s="17" t="n">
         <x:v>108.69</x:v>
       </x:c>
       <x:c r="K59" t="str">
@@ -3638,7 +3665,7 @@
       <x:c r="I60" s="9" t="n">
         <x:v>100000</x:v>
       </x:c>
-      <x:c r="J60" s="14" t="n">
+      <x:c r="J60" s="17" t="n">
         <x:v>1.138</x:v>
       </x:c>
       <x:c r="K60" t="str">
@@ -3688,7 +3715,7 @@
       <x:c r="I61" s="9" t="n">
         <x:v>-100000</x:v>
       </x:c>
-      <x:c r="J61" s="14" t="n">
+      <x:c r="J61" s="17" t="n">
         <x:v>0.8581</x:v>
       </x:c>
       <x:c r="K61" t="str">
@@ -3738,7 +3765,7 @@
       <x:c r="I62" s="9" t="n">
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="J62" s="14" t="n">
+      <x:c r="J62" s="17" t="n">
         <x:v>8.9142</x:v>
       </x:c>
       <x:c r="K62" t="str">
@@ -3788,7 +3815,7 @@
       <x:c r="I63" s="9" t="n">
         <x:v>10000000</x:v>
       </x:c>
-      <x:c r="J63" s="14" t="n">
+      <x:c r="J63" s="17" t="n">
         <x:v>108.74</x:v>
       </x:c>
       <x:c r="K63" t="str">
@@ -3838,7 +3865,7 @@
       <x:c r="I64" s="9" t="n">
         <x:v>800000</x:v>
       </x:c>
-      <x:c r="J64" s="14" t="n">
+      <x:c r="J64" s="17" t="n">
         <x:v>7.6969</x:v>
       </x:c>
       <x:c r="K64" t="str">
@@ -3888,7 +3915,7 @@
       <x:c r="I65" s="9" t="n">
         <x:v>350000</x:v>
       </x:c>
-      <x:c r="J65" s="14" t="n">
+      <x:c r="J65" s="17" t="n">
         <x:v>1.646905</x:v>
       </x:c>
       <x:c r="K65" t="str">
@@ -3938,7 +3965,7 @@
       <x:c r="I66" s="9" t="n">
         <x:v>-150000</x:v>
       </x:c>
-      <x:c r="J66" s="14" t="n">
+      <x:c r="J66" s="17" t="n">
         <x:v>0.8582</x:v>
       </x:c>
       <x:c r="K66" t="str">
@@ -3988,7 +4015,7 @@
       <x:c r="I67" s="9" t="n">
         <x:v>18000000</x:v>
       </x:c>
-      <x:c r="J67" s="14" t="n">
+      <x:c r="J67" s="17" t="n">
         <x:v>109.51</x:v>
       </x:c>
       <x:c r="K67" t="str">
@@ -4038,7 +4065,7 @@
       <x:c r="I68" s="9" t="n">
         <x:v>300000</x:v>
       </x:c>
-      <x:c r="J68" s="14" t="n">
+      <x:c r="J68" s="17" t="n">
         <x:v>4.306</x:v>
       </x:c>
       <x:c r="K68" t="str">
@@ -4088,7 +4115,7 @@
       <x:c r="I69" s="9" t="n">
         <x:v>2500000</x:v>
       </x:c>
-      <x:c r="J69" s="14" t="n">
+      <x:c r="J69" s="17" t="n">
         <x:v>7.7362</x:v>
       </x:c>
       <x:c r="K69" t="str">
@@ -4138,7 +4165,7 @@
       <x:c r="I70" s="9" t="n">
         <x:v>950000</x:v>
       </x:c>
-      <x:c r="J70" s="14" t="n">
+      <x:c r="J70" s="17" t="n">
         <x:v>4.3081</x:v>
       </x:c>
       <x:c r="K70" t="str">
@@ -4188,7 +4215,7 @@
       <x:c r="I71" s="9" t="n">
         <x:v>2000000</x:v>
       </x:c>
-      <x:c r="J71" s="14" t="n">
+      <x:c r="J71" s="17" t="n">
         <x:v>8.999</x:v>
       </x:c>
       <x:c r="K71" t="str">
@@ -4238,7 +4265,7 @@
       <x:c r="I72" s="9" t="n">
         <x:v>-120000</x:v>
       </x:c>
-      <x:c r="J72" s="14" t="n">
+      <x:c r="J72" s="17" t="n">
         <x:v>1.4765</x:v>
       </x:c>
       <x:c r="K72" t="str">
@@ -4288,7 +4315,7 @@
       <x:c r="I73" s="9" t="n">
         <x:v>1000000</x:v>
       </x:c>
-      <x:c r="J73" s="14" t="n">
+      <x:c r="J73" s="17" t="n">
         <x:v>7.7663</x:v>
       </x:c>
       <x:c r="K73" t="str">
@@ -4338,7 +4365,7 @@
       <x:c r="I74" s="9" t="n">
         <x:v>800000</x:v>
       </x:c>
-      <x:c r="J74" s="14" t="n">
+      <x:c r="J74" s="17" t="n">
         <x:v>9.0317</x:v>
       </x:c>
       <x:c r="K74" t="str">
@@ -4388,7 +4415,7 @@
       <x:c r="I75" s="9" t="n">
         <x:v>2500000</x:v>
       </x:c>
-      <x:c r="J75" s="14" t="n">
+      <x:c r="J75" s="17" t="n">
         <x:v>38.17</x:v>
       </x:c>
       <x:c r="K75" t="str">
@@ -4438,7 +4465,7 @@
       <x:c r="I76" s="9" t="n">
         <x:v>480000</x:v>
       </x:c>
-      <x:c r="J76" s="14" t="n">
+      <x:c r="J76" s="17" t="n">
         <x:v>1.152305</x:v>
       </x:c>
       <x:c r="K76" t="str">
@@ -4488,7 +4515,7 @@
       <x:c r="I77" s="9" t="n">
         <x:v>670000000</x:v>
       </x:c>
-      <x:c r="J77" s="14" t="n">
+      <x:c r="J77" s="17" t="n">
         <x:v>1636</x:v>
       </x:c>
       <x:c r="K77" t="str">
@@ -4538,7 +4565,7 @@
       <x:c r="I78" s="9" t="n">
         <x:v>-17400000</x:v>
       </x:c>
-      <x:c r="J78" s="14" t="n">
+      <x:c r="J78" s="17" t="n">
         <x:v>110.68</x:v>
       </x:c>
       <x:c r="K78" t="str">
@@ -4588,7 +4615,7 @@
       <x:c r="I79" s="9" t="n">
         <x:v>450000</x:v>
       </x:c>
-      <x:c r="J79" s="14" t="n">
+      <x:c r="J79" s="17" t="n">
         <x:v>1.159737</x:v>
       </x:c>
       <x:c r="K79" t="str">
